--- a/artfynd/A 9214-2023 artfynd.xlsx
+++ b/artfynd/A 9214-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 9214-2023 artfynd.xlsx
+++ b/artfynd/A 9214-2023 artfynd.xlsx
@@ -818,7 +818,7 @@
         <v>117845129</v>
       </c>
       <c r="B3" t="n">
-        <v>97742</v>
+        <v>97744</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 9214-2023 artfynd.xlsx
+++ b/artfynd/A 9214-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -808,139 +808,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>117845129</v>
-      </c>
-      <c r="B3" t="n">
-        <v>97746</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>504</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Guckusko</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Cypripedium calceolus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Syninge, mellan Eksättra och Tylan (*gk* /stjälk/), Upl</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>698599</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6630418</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Norrtälje</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Husby-Sjuhundra</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>AB-Nor-0982</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2024-06-15</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2024-06-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>13 blommande stjälkar. Två bestånd 20-30 m från varandra. Biotopen såg ej bra ut då den låg i utkanten av ett stort hygga.</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Jan Yngve Andersson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Jan Yngve Andersson, Lina Wirén, Eva-Mariann Brunkener</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
